--- a/tools/事件总表_代码实装.xlsx
+++ b/tools/事件总表_代码实装.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>闲聊</t>
+          <t>闲聊（含加入）</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -526,12 +526,12 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>双方空闲、同空间</t>
+          <t>双方空闲、同空间；加入另需 A(i,j)≥30、我压力&lt;80（软门槛）</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>发起无判定；加入：score=A[j][i]+外向度修正，p=σ((score−43)/10)，对方压力≥12 压制 score；加入尝试 10 tick</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
@@ -543,7 +543,7 @@
       <c r="H2" s="2" t="inlineStr">
         <is>
           <t>① 双方标记 in_conversation
-② 互相占用时间槽
+② 互相占用时间槽（加入：全体成员与结束点对齐）
 ③ 双向施加 topic_affinity/trust/stress
 ④ 双向 observe 亲和
 ⑤ 登记/并入活动会话</t>
@@ -556,96 +556,44 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>加入被拒: affinity−3, hostility+3, stress+2 + observe</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>join_chat</t>
+          <t>tease</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>搭话/加入闲聊</t>
+          <t>当众调侃</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>同 chat 入口</t>
+          <t>base_p=0.09/tick</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>决策侧: A(i,j)≥30(软门槛)
-我压力&lt;80(软门槛)</t>
+          <t>需≥3人围观(共同邻居)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>score = A[j][i] + 外向度修正
-p = sigmoid((score−43)/10)
-对方压力≥12时压制score</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>【接受】委托给 chat 执行
-【拒绝】请求者获得 reject 三轴事件 + observe</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>同 chat 加点</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>affinity−3, hostility+3, stress+2</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>tease</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>当众调侃</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>base_p=0.09/tick</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>需≥3人围观(共同邻居)</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>笑场档: A(i,j)≥55 且 H(i,j)&lt;25
 嘲讽档: H(i,j)≥40 或 A(i,j)&lt;25</t>
         </is>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F3" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G3" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>【笑场】双方+success_affinity, 围观者对j+affinity, 目标stress−2
 【嘲讽】目标+hostility/stress, 围观者站队判定
@@ -654,36 +602,36 @@
   围观者≥4人→升级羞辱(mark_hurt, 写深层敌意)</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>笑场: 双方affinity+2, 目标stress−2</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>嘲讽: 目标hostility+3, stress+3
 羞辱额外: hostility+4(深层)</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>report</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>举报</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>base_p=0.10 × sigmoid(z)
 每段课间对有把柄候选掷骰</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>H(i,j)≥40(sigmoid拐点)
 scale≥8
@@ -692,171 +640,120 @@
 信任惩罚: T/100×1.0压低z</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>sigmoid: H(i,j)拐点40, scale=8</t>
         </is>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F4" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="G4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>① 目标获得 report_stress + report_hostility(对举报者)
 ② mark_hurt(i,j) 记录伤害
 ③ 举报者 hostility 降低</t>
         </is>
       </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>目标: stress+5(major), hostility+5(major)</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>roughhouse</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>追逐打闹</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>base_p=0.05/tick</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>发起者外向度E≥45
+旁观者人数≥2</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>① 双方互相+roughhouse_affinity
+② 所有旁观者对双方+roughhouse_hostility</t>
+        </is>
+      </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>目标: stress+5(major), hostility+5(major)</t>
+          <t>参与者双向: affinity+2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>旁观者: hostility+3(对参与者)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>rumor</t>
+          <t>exclude</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>流言</t>
+          <t>排挤</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>base_p=0.03/tick</t>
+          <t>base_p=0.06/tick</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>有交互目标</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>方向判定: H(i,j)&gt;A(i,j)→负面</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>① 判断方向(负面/正面)
-② 目标对传播者+rumor_hostility
-③ 负面时: 发起者+rumor_stress+tease_hostility
-④ 全场其他节点 observe j 的 hostility</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>目标: hostility+3</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>负面时发起者: stress+3, hostility+3</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>roughhouse</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>追逐打闹</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>base_p=0.05/tick</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>发起者外向度E≥45
-旁观者人数≥2</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>① 双方互相+roughhouse_affinity
-② 所有旁观者对双方+roughhouse_hostility</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>参与者双向: affinity+2</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>旁观者: hostility+3(对参与者)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>exclude</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>排挤</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>base_p=0.06/tick</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>近30天内有敌对行为
 cooldown≥7天
 ≥3人集体(≥2人有重大敌对)</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F6" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="G6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>① 目标对发起者+exclude_stress+exclude_affinity
 ② 目标对所有crowd成员−affinity
@@ -865,171 +762,171 @@
 (双向好感下降)</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>目标: stress+5(major)
 双向: affinity−4(major)</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>comfort</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>安慰</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>base_p=0.35/tick
 (高概率因命中条件极窄)</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>目标stress≥70
 好感门槛: E≥50→≥50, E=0→≥70
 (线性插值)</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>好感门槛 = 50 + (50−E)/50 × 20</t>
         </is>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="F7" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="G7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>① 发起者付 comfort_cost_stress
 ② 目标: stress−5, affinity+4, trust+5</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>目标: stress−5(major), affinity+4(major), trust+5(major)</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>发起者成本: stress+2</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>ask_help</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>求助</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>base_p=0.04/tick</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>好感门槛: E=50→≥30, E=0→≥50, E=100→≥20
 (线性插值)</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>score = A[j][i] + E_j/100×10
 p = sigmoid((score−40)/12)</t>
         </is>
       </c>
-      <c r="F10" s="2" t="n">
+      <c r="F8" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="G10" s="2" t="n">
+      <c r="G8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>【接受】① 发起者付cost → ② 求助者affinity+3, stress−2 → ③ 帮忙者affinity+2, trust+3
 【拒绝】① 发起者付cost → ② 求助者stress+3, hostility+3, trust−3</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>求助者: affinity+3, stress−2
 帮忙者: affinity+2, trust+3</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>求助者: stress+3, hostility+3, trust−3
 (发起成本: stress+2)</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>apologize</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>道歉和解</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>base_p=0.05/tick</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>真值H(i,j)≥30
 信念B_H(i,j)≥30
 (决策侧不得读对方真值)</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>score = A[j][i] + F_j/100×20 − H[j][i]×0.5
 p = sigmoid((score−40)/12)
 no_modulation=true(跳过关系调制)</t>
         </is>
       </c>
-      <c r="F11" s="2" t="n">
+      <c r="F9" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="G11" s="2" t="n">
+      <c r="G9" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>【接受】① 发起者付cost → ② 双向hostility−3(只消表层), affinity+3, trust+2, stress−3
 【拒绝】① 发起者付cost → ② hostility+2, stress+4(major), trust−3</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>双向: hostility−3, affinity+3, trust+2, stress−3</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>hostility+2, stress+4(major), trust−3
 (发起成本: stress+3)</t>
@@ -1047,7 +944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1276,7 +1173,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>闲聊的不可窃听/不可被搭话版本(无声)</t>
+          <t>闲聊的不可被加入版本(无声)</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1288,12 +1185,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>inform</t>
+          <t>observe</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>告密</t>
+          <t>观察</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1303,15 +1200,19 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>把掌握的流言单独告诉目标</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>20</v>
+          <t>玩家独有；靠近单人或活动圈</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>≥ 10</t>
+        </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>无法被窃听(低声)</t>
+          <t>只读信息，零副作用
+单人 2 真值 + 1 信念（O ≥ 50 再多 1）
+群体对圈内每人各 1+1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1323,12 +1224,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>ask_about</t>
+          <t>share_secret</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>打听</t>
+          <t>秘密交换</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1338,55 +1239,19 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>玩家独有</t>
+          <t>双方信任≥60</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>向某人打听另一人的事
-透露度 = 他对你的信任(信念矩阵)</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>share_secret</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>秘密交换</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>双方信任≥60</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>守密超5tick→形成secret_alliance标签
 泄密→信任崩塌</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>守密: 双方每日trust+1(7天)
 泄密: stress+5, trust−5, hostility+4</t>
@@ -1404,7 +1269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2440,12 +2305,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>rumor_hostility</t>
+          <t>topic_trust</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>hostility</t>
+          <t>trust</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
@@ -2455,13 +2320,13 @@
         <v>0</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>0.2</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -2470,40 +2335,40 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>被传谣:对传播者敌对↑</t>
+          <t>话题共鸣</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>rumor_stress</t>
+          <t>topic_affinity</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>stress</t>
+          <t>affinity</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v>3</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -2512,34 +2377,34 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>被流言击中:压力↑</t>
+          <t>话题共鸣</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>topic_trust</t>
+          <t>topic_stress</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>trust</t>
+          <t>stress</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>0.2</v>
@@ -2566,25 +2431,25 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>topic_affinity</t>
+          <t>comfort_cost_stress</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>affinity</t>
+          <t>stress</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>0.2</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>0</v>
@@ -2601,14 +2466,14 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>话题共鸣</t>
+          <t>安慰发起成本</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>topic_stress</t>
+          <t>ask_help_cost_stress</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -2617,17 +2482,17 @@
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="D29" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="2" t="n">
         <v>0.3</v>
       </c>
-      <c r="E29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="2" t="n">
-        <v>0.2</v>
-      </c>
       <c r="G29" s="2" t="n">
         <v>0</v>
       </c>
@@ -2638,38 +2503,38 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>话题共鸣</t>
+          <t>求助发起成本</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>comfort_cost_stress</t>
+          <t>ask_help_ok_asker_affinity</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>stress</t>
+          <t>affinity</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="E30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>0.3</v>
-      </c>
       <c r="G30" s="2" t="n">
         <v>0</v>
       </c>
@@ -2680,19 +2545,19 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>安慰发起成本</t>
+          <t>求助成功:求助者好感↑</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>ask_help_cost_stress</t>
+          <t>ask_help_ok_asker_stress</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -2701,7 +2566,7 @@
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>0.2</v>
@@ -2727,14 +2592,14 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>求助发起成本</t>
+          <t>求助成功:求助者压力↓</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>ask_help_ok_asker_affinity</t>
+          <t>ask_help_ok_helper_affinity</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -2743,7 +2608,7 @@
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>0</v>
@@ -2752,7 +2617,7 @@
         <v>0</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>0</v>
@@ -2769,33 +2634,33 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>求助成功:求助者好感↑</t>
+          <t>求助成功:帮忙者好感↑</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>ask_help_ok_asker_stress</t>
+          <t>ask_help_ok_helper_trust</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>stress</t>
+          <t>trust</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="D33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="E33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="2" t="n">
-        <v>0.3</v>
-      </c>
       <c r="G33" s="2" t="n">
         <v>0</v>
       </c>
@@ -2811,26 +2676,26 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>求助成功:求助者压力↓</t>
+          <t>求助成功:帮忙者信任↑</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>ask_help_ok_helper_affinity</t>
+          <t>ask_help_no_stress</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>affinity</t>
+          <t>stress</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E34" s="2" t="n">
         <v>0</v>
@@ -2853,19 +2718,19 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>求助成功:帮忙者好感↑</t>
+          <t>求助被拒:压力↑</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>ask_help_ok_helper_trust</t>
+          <t>ask_help_no_hostility</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>trust</t>
+          <t>hostility</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
@@ -2881,7 +2746,7 @@
         <v>0.2</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -2895,33 +2760,33 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>求助成功:帮忙者信任↑</t>
+          <t>求助被拒:敌对↑</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>ask_help_no_stress</t>
+          <t>ask_help_no_trust</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>stress</t>
+          <t>trust</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="D36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="E36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" s="2" t="n">
-        <v>0.3</v>
-      </c>
       <c r="G36" s="2" t="n">
         <v>0</v>
       </c>
@@ -2937,19 +2802,19 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>求助被拒:压力↑</t>
+          <t>求助被拒:信任↓</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>ask_help_no_hostility</t>
+          <t>apologize_cost_stress</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>hostility</t>
+          <t>stress</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
@@ -2962,10 +2827,10 @@
         <v>0</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2974,24 +2839,24 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>求助被拒:敌对↑</t>
+          <t>道歉发起成本</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>ask_help_no_trust</t>
+          <t>apologize_ok_hostility</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>trust</t>
+          <t>hostility</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
@@ -3004,11 +2869,11 @@
         <v>0</v>
       </c>
       <c r="F38" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G38" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="G38" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
           <t>normal</t>
@@ -3016,24 +2881,24 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>求助被拒:信任↓</t>
+          <t>道歉被接受:只消表层敌对</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>apologize_cost_stress</t>
+          <t>apologize_ok_affinity</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>stress</t>
+          <t>affinity</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
@@ -3063,23 +2928,23 @@
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>道歉发起成本</t>
+          <t>道歉被接受:好感回升(双向)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>apologize_ok_hostility</t>
+          <t>apologize_ok_trust</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>hostility</t>
+          <t>trust</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>-3</v>
+        <v>2</v>
       </c>
       <c r="D40" s="2" t="n">
         <v>0</v>
@@ -3088,10 +2953,10 @@
         <v>0</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -3105,23 +2970,23 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>道歉被接受:只消表层敌对</t>
+          <t>道歉被接受:信任回升(双向)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>apologize_ok_affinity</t>
+          <t>apologize_ok_stress</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>affinity</t>
+          <t>stress</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="D41" s="2" t="n">
         <v>0</v>
@@ -3147,19 +3012,19 @@
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>道歉被接受:好感回升(双向)</t>
+          <t>道歉被接受:双方松口气</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>apologize_ok_trust</t>
+          <t>apologize_no_hostility</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>trust</t>
+          <t>hostility</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
@@ -3172,11 +3037,11 @@
         <v>0</v>
       </c>
       <c r="F42" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G42" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="G42" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
           <t>normal</t>
@@ -3189,14 +3054,14 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>道歉被接受:信任回升(双向)</t>
+          <t>道歉被拒:敌对继续</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>apologize_ok_stress</t>
+          <t>apologize_no_stress</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -3205,7 +3070,7 @@
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
       <c r="D43" s="2" t="n">
         <v>0</v>
@@ -3214,14 +3079,14 @@
         <v>0</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>major</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -3231,23 +3096,23 @@
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>道歉被接受:双方松口气</t>
+          <t>道歉被拒:重大档</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>apologize_no_hostility</t>
+          <t>apologize_no_trust</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>hostility</t>
+          <t>trust</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="D44" s="2" t="n">
         <v>0</v>
@@ -3256,10 +3121,10 @@
         <v>0</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -3272,90 +3137,6 @@
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>道歉被拒:敌对继续</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>apologize_no_stress</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>stress</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="D45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G45" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>major</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>道歉被拒:重大档</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>apologize_no_trust</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>trust</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="n">
-        <v>-3</v>
-      </c>
-      <c r="D46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
         <is>
           <t>道歉被拒:信任受损</t>
         </is>
@@ -3858,12 +3639,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>join_chat</t>
+          <t>chat</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>affinity</t>
+          <t>join_affinity</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -3883,12 +3664,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>join_chat</t>
+          <t>chat</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>scale</t>
+          <t>join_scale</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -3908,12 +3689,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>join_chat</t>
+          <t>chat</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>stress_penalty</t>
+          <t>join_stress_penalty</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -3933,12 +3714,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>join_chat</t>
+          <t>chat</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>gate_affinity</t>
+          <t>join_gate_affinity</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -3958,12 +3739,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>join_chat</t>
+          <t>chat</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>gate_stress</t>
+          <t>join_gate_stress</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">

--- a/tools/事件总表_代码实装.xlsx
+++ b/tools/事件总表_代码实装.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -829,104 +829,51 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>ask_help</t>
+          <t>apologize</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>求助</t>
+          <t>道歉和解</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>base_p=0.04/tick</t>
+          <t>base_p=0.05/tick</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>好感门槛: E=50→≥30, E=0→≥50, E=100→≥20
-(线性插值)</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>score = A[j][i] + E_j/100×10
-p = sigmoid((score−40)/12)</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>【接受】① 发起者付cost → ② 求助者affinity+3, stress−2 → ③ 帮忙者affinity+2, trust+3
-【拒绝】① 发起者付cost → ② 求助者stress+3, hostility+3, trust−3</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>求助者: affinity+3, stress−2
-帮忙者: affinity+2, trust+3</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>求助者: stress+3, hostility+3, trust−3
-(发起成本: stress+2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>apologize</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>道歉和解</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>base_p=0.05/tick</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>真值H(i,j)≥30
 信念B_H(i,j)≥30
 (决策侧不得读对方真值)</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>score = A[j][i] + F_j/100×20 − H[j][i]×0.5
 p = sigmoid((score−40)/12)
 no_modulation=true(跳过关系调制)</t>
         </is>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="F8" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="G8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>【接受】① 发起者付cost → ② 双向hostility−3(只消表层), affinity+3, trust+2, stress−3
 【拒绝】① 发起者付cost → ② hostility+2, stress+4(major), trust−3</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>双向: hostility−3, affinity+3, trust+2, stress−3</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>hostility+2, stress+4(major), trust−3
 (发起成本: stress+3)</t>
@@ -1269,7 +1216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J44"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2473,7 +2420,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>ask_help_cost_stress</t>
+          <t>apologize_cost_stress</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -2482,10 +2429,10 @@
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E29" s="2" t="n">
         <v>0</v>
@@ -2503,28 +2450,28 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>求助发起成本</t>
+          <t>道歉发起成本</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>ask_help_ok_asker_affinity</t>
+          <t>apologize_ok_hostility</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>affinity</t>
+          <t>hostility</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>0</v>
@@ -2533,11 +2480,11 @@
         <v>0</v>
       </c>
       <c r="F30" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G30" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="G30" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
           <t>normal</t>
@@ -2545,31 +2492,31 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>求助成功:求助者好感↑</t>
+          <t>道歉被接受:只消表层敌对</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>ask_help_ok_asker_stress</t>
+          <t>apologize_ok_affinity</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>stress</t>
+          <t>affinity</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E31" s="2" t="n">
         <v>0</v>
@@ -2587,24 +2534,24 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>求助成功:求助者压力↓</t>
+          <t>道歉被接受:好感回升(双向)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>ask_help_ok_helper_affinity</t>
+          <t>apologize_ok_trust</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>affinity</t>
+          <t>trust</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
@@ -2617,7 +2564,7 @@
         <v>0</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>0</v>
@@ -2629,28 +2576,28 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>求助成功:帮忙者好感↑</t>
+          <t>道歉被接受:信任回升(双向)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>ask_help_ok_helper_trust</t>
+          <t>apologize_ok_stress</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>trust</t>
+          <t>stress</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="D33" s="2" t="n">
         <v>0</v>
@@ -2659,7 +2606,7 @@
         <v>0</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>0</v>
@@ -2671,31 +2618,31 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>求助成功:帮忙者信任↑</t>
+          <t>道歉被接受:双方松口气</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>ask_help_no_stress</t>
+          <t>apologize_no_hostility</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>stress</t>
+          <t>hostility</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E34" s="2" t="n">
         <v>0</v>
@@ -2704,7 +2651,7 @@
         <v>0.3</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2713,28 +2660,28 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>求助被拒:压力↑</t>
+          <t>道歉被拒:敌对继续</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>ask_help_no_hostility</t>
+          <t>apologize_no_stress</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>hostility</t>
+          <t>stress</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D35" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2690,31 @@
         <v>0</v>
       </c>
       <c r="F35" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G35" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="G35" s="2" t="n">
-        <v>0.3</v>
-      </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>major</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>求助被拒:敌对↑</t>
+          <t>道歉被拒:重大档</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>ask_help_no_trust</t>
+          <t>apologize_no_trust</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2797,346 +2744,10 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>求助被拒:信任↓</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>apologize_cost_stress</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>stress</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>道歉发起成本</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>apologize_ok_hostility</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>hostility</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="n">
-        <v>-3</v>
-      </c>
-      <c r="D38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G38" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>道歉被接受:只消表层敌对</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>apologize_ok_affinity</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>affinity</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>道歉被接受:好感回升(双向)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>apologize_ok_trust</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>trust</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>道歉被接受:信任回升(双向)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>apologize_ok_stress</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>stress</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="n">
-        <v>-3</v>
-      </c>
-      <c r="D41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>道歉被接受:双方松口气</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>apologize_no_hostility</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>hostility</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G42" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>道歉被拒:敌对继续</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>apologize_no_stress</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>stress</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="D43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G43" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>major</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>道歉被拒:重大档</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>apologize_no_trust</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>trust</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="n">
-        <v>-3</v>
-      </c>
-      <c r="D44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
         <is>
           <t>道歉被拒:信任受损</t>
         </is>
@@ -3299,7 +2910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4014,12 +3625,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>ask_help</t>
+          <t>apologize</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>affinity</t>
+          <t>accept_scale</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -4028,23 +3639,23 @@
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>求助好感门槛(E=50)</t>
+          <t>sigmoid 坡度</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>ask_help</t>
+          <t>apologize</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>introvert_affinity</t>
+          <t>calm_bonus</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -4053,23 +3664,23 @@
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>求助好感门槛(E=0)</t>
+          <t>对方随和系数</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>ask_help</t>
+          <t>apologize</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>extrovert_affinity</t>
+          <t>hostility_penalty</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -4078,184 +3689,9 @@
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>20</v>
+        <v>0.5</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>求助好感门槛(E=100)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>ask_help</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>accept_theta</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>&gt;=</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>求助接纳 sigmoid 拐点</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>ask_help</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>accept_scale</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>&gt;=</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>sigmoid 坡度</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>ask_help</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>extrovert_bonus</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>&gt;=</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>被求助者外向度加成</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>apologize</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>accept_theta</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>&gt;=</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>道歉接纳 sigmoid 拐点</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>apologize</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>accept_scale</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>&gt;=</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>sigmoid 坡度</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>apologize</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>calm_bonus</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>&gt;=</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>对方随和系数</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>apologize</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>hostility_penalty</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>&gt;=</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>敌对压制系数</t>
         </is>

--- a/tools/事件总表_代码实装.xlsx
+++ b/tools/事件总表_代码实装.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -509,38 +509,86 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>observe</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>观察</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>玩家主动（无概率；NPC 不做）</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>玩家空闲；靠近对象（1.2 m / 同列前后邻座 1.8 m）；对象活动剩余 ≥10 tick</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>无判定（只读，不掷骰）</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>读对象对玩家的真实态度 A／H（O ≥ 50 再加 T）＋他的误判（B[对象][玩家]）；结果进情报提示</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>零副作用：不写矩阵、不发声、不占用也不打断对象</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
           <t>chat</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>闲聊（含加入）</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>base_p=0.06/tick
 相邻×1.5
 压力≥70时×0.5</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>双方空闲、同空间；加入另需 A(i,j)≥30、我压力&lt;80（软门槛）</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>发起无判定；加入：score=A[j][i]+外向度修正，p=σ((score−43)/10)，对方压力≥12 压制 score；加入尝试 10 tick</t>
         </is>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F3" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>① 双方标记 in_conversation
 ② 互相占用时间槽（加入：全体成员与结束点对齐）
@@ -549,51 +597,51 @@
 ⑤ 登记/并入活动会话</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>双向: affinity+3, trust+3, stress−2</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>加入被拒: affinity−3, hostility+3, stress+2 + observe</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>tease</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>当众调侃</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>base_p=0.09/tick</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>需≥3人围观(共同邻居)</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>笑场档: A(i,j)≥55 且 H(i,j)&lt;25
 嘲讽档: H(i,j)≥40 或 A(i,j)&lt;25</t>
         </is>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F4" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="G4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>【笑场】双方+success_affinity, 围观者对j+affinity, 目标stress−2
 【嘲讽】目标+hostility/stress, 围观者站队判定
@@ -602,36 +650,36 @@
   围观者≥4人→升级羞辱(mark_hurt, 写深层敌意)</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>笑场: 双方affinity+2, 目标stress−2</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>嘲讽: 目标hostility+3, stress+3
 羞辱额外: hostility+4(深层)</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>report</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>举报</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>base_p=0.10 × sigmoid(z)
 每段课间对有把柄候选掷骰</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>H(i,j)≥40(sigmoid拐点)
 scale≥8
@@ -640,120 +688,120 @@
 信任惩罚: T/100×1.0压低z</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>sigmoid: H(i,j)拐点40, scale=8</t>
         </is>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F5" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>① 目标获得 report_stress + report_hostility(对举报者)
 ② mark_hurt(i,j) 记录伤害
 ③ 举报者 hostility 降低</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>目标: stress+5(major), hostility+5(major)</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>roughhouse</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>追逐打闹</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>base_p=0.05/tick</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>发起者外向度E≥45
 旁观者人数≥2</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F6" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="G6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>① 双方互相+roughhouse_affinity
 ② 所有旁观者对双方+roughhouse_hostility</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>参与者双向: affinity+2</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>旁观者: hostility+3(对参与者)</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>exclude</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>排挤</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>base_p=0.06/tick</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>近30天内有敌对行为
 cooldown≥7天
 ≥3人集体(≥2人有重大敌对)</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F7" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="G7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>① 目标对发起者+exclude_stress+exclude_affinity
 ② 目标对所有crowd成员−affinity
@@ -762,118 +810,118 @@
 (双向好感下降)</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>目标: stress+5(major)
 双向: affinity−4(major)</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>comfort</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>安慰</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>base_p=0.35/tick
 (高概率因命中条件极窄)</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>目标stress≥70
 好感门槛: E≥50→≥50, E=0→≥70
 (线性插值)</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>好感门槛 = 50 + (50−E)/50 × 20</t>
         </is>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="F8" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="G8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>① 发起者付 comfort_cost_stress
 ② 目标: stress−5, affinity+4, trust+5</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>目标: stress−5(major), affinity+4(major), trust+5(major)</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>发起者成本: stress+2</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>apologize</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>道歉和解</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>base_p=0.05/tick</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>真值H(i,j)≥30
 信念B_H(i,j)≥30
 (决策侧不得读对方真值)</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>score = A[j][i] + F_j/100×20 − H[j][i]×0.5
 p = sigmoid((score−40)/12)
 no_modulation=true(跳过关系调制)</t>
         </is>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F9" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="G9" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>【接受】① 发起者付cost → ② 双向hostility−3(只消表层), affinity+3, trust+2, stress−3
 【拒绝】① 发起者付cost → ② hostility+2, stress+4(major), trust−3</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>双向: hostility−3, affinity+3, trust+2, stress−3</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>hostility+2, stress+4(major), trust−3
 (发起成本: stress+3)</t>
